--- a/docs/jamii-jira-plan.xlsx
+++ b/docs/jamii-jira-plan.xlsx
@@ -13,7 +13,7 @@
     <sheet name="How to import" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Jira Import'!$A$1:$O$90</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Jira Import'!$A$1:$O$94</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="362">
   <si>
     <t xml:space="preserve">By epic</t>
   </si>
@@ -72,6 +72,12 @@
     <t xml:space="preserve">STRETCH: Edge, nginx and subdomains</t>
   </si>
   <si>
+    <t xml:space="preserve">E14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mock backends (Spring Boot)</t>
+  </si>
+  <si>
     <t xml:space="preserve">E3</t>
   </si>
   <si>
@@ -384,22 +390,13 @@
     <t xml:space="preserve">Temurin + H2 jar; RunScript schema and seed, then TCP server on 9092; healthcheck. AC: MI datasource connects.</t>
   </si>
   <si>
-    <t xml:space="preserve">S2.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build jamii/wiremock image</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stubs mirroring the Beeceptor customer rules and DNE Divide, plus fault scenarios (delay, reset, SOAP fault). AC: stubs answer on 8089 and match beeceptor-rules.json.</t>
-  </si>
-  <si>
     <t xml:space="preserve">S2.9</t>
   </si>
   <si>
     <t xml:space="preserve">docker-compose.yml with profiles</t>
   </si>
   <si>
-    <t xml:space="preserve">Services, jamii-net network, healthchecks, depends_on; profiles core, observability, ci. AC: compose --profile core up is healthy.</t>
+    <t xml:space="preserve">Services, jamii-net network plus external jamii-shared (created by the mock backends), healthchecks, depends_on; profiles core, observability, ci. AC: compose --profile core up is healthy.</t>
   </si>
   <si>
     <t xml:space="preserve">S2.10</t>
@@ -459,6 +456,60 @@
     <t xml:space="preserve">Confirm MI 8290, Elasticsearch, H2 and registry are unreachable from outside the Docker network. AC: evidence in README.</t>
   </si>
   <si>
+    <t xml:space="preserve">Separate Spring Boot service mocking the customer system (REST) and credit-check engine (SOAP). JDK 21, Maven, jar; own Dockerfile and compose; deployed separately.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mock-backends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mock backends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S14.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create jamii-mock-backends repository</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Push the generated project (pom, sources, tests, Dockerfile, compose, README) to its own Git repo. AC: repo public or shared with the panel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S14.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build and test the jar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvn clean package on JDK 21 (first compile of the generated code); fix any build or test failures. AC: jar built, 17 tests green (incl. full-context test for OpenAPI, WSDL and Swagger UI); logs show REQUEST_IN and RESPONSE_OUT with masked PII.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S14.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build image and run with compose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">docker compose up -d --build; creates the jamii-shared network; health UP. AC: curl customers 1001/9999/5000, WSDL, Swagger UI and one SOAP call all behave per rules.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S14.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deploy mock backends to the target host</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deploy separately; record the URL for CUSTOMER_BACKEND_URL and CREDIT_BACKEND_URL. AC: MI can reach both endpoints.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S14.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hand contract to MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy credit-check.xsd/WSDL into the MI loan module as a reference; agree customer JSON shape. AC: MI mapping built against the published contract.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Shared sequences, templates and class mediator used by all three APIs.</t>
   </si>
   <si>
@@ -576,7 +627,7 @@
     <t xml:space="preserve">MI unit test suite for 200, 400, 404 against the H2 container. AC: tests run in mvn build.</t>
   </si>
   <si>
-    <t xml:space="preserve">Managed proxy in front of a Beeceptor mock endpoint with gateway value; WireMock mirror for CI.</t>
+    <t xml:space="preserve">Managed proxy in front of the Jamii mock customer service (Spring Boot) with gateway value.</t>
   </si>
   <si>
     <t xml:space="preserve">customer-api</t>
@@ -591,16 +642,7 @@
     <t xml:space="preserve">CustomerBackendEP</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP endpoint with 5 s timeout and configurable base URL (Beeceptor for demo, WireMock for CI). AC: switch backend by env var only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S5.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beeceptor endpoint and rules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create the Beeceptor endpoint; rules for /customers/1001-1005 (200, bank-shaped records with national ID, +254 phone, KYC status), 9999 (404), 5000 (500), 5004 (7 s delay); export to mocks/beeceptor-rules.json; check free-tier quota. AC: all four rules answer; export committed.</t>
+    <t xml:space="preserve">HTTP endpoint with 5 s timeout; base URL from CUSTOMER_BACKEND_URL (jamii-mock-backends). AC: switch backend by env var only.</t>
   </si>
   <si>
     <t xml:space="preserve">S5.2</t>
@@ -618,10 +660,10 @@
     <t xml:space="preserve">Customer API tests</t>
   </si>
   <si>
-    <t xml:space="preserve">MI unit test suite with a mock service for CustomerBackendEP (200, 404, 5xx); WireMock delay for 504. AC: 404, 503 and 504 proven.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REST/JSON to SOAP (DNE Calculator Divide) with fault mapping.</t>
+    <t xml:space="preserve">MI unit test suite with a mock service for CustomerBackendEP (200, 404, 5xx); mock backends rule 5004 (7 s) for 504. AC: 404, 502, 503 and 504 proven.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REST/JSON to SOAP (mock credit-check CheckEligibility) with fault mapping.</t>
   </si>
   <si>
     <t xml:space="preserve">loan-api</t>
@@ -642,10 +684,10 @@
     <t xml:space="preserve">S6.2</t>
   </si>
   <si>
-    <t xml:space="preserve">JSON to SOAP Divide mapping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intA = (existingMonthlyDebt + requestedMonthlyInstalment) x 100; intB = monthlyIncome. AC: correct SOAP envelope logged (masked).</t>
+    <t xml:space="preserve">JSON to SOAP CheckEligibility mapping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PayloadFactory maps the four JSON fields 1:1 to CheckEligibilityRequest (namespace http://jamii.daqiqtech.co.ke/credit/v1). AC: correct SOAP envelope logged (masked).</t>
   </si>
   <si>
     <t xml:space="preserve">S6.3</t>
@@ -654,7 +696,7 @@
     <t xml:space="preserve">SOAP to JSON decision</t>
   </si>
   <si>
-    <t xml:space="preserve">DivideResult = DTI %; ELIGIBLE when 40 or less; response per SDD 4.3. AC: clean JSON, no XML.</t>
+    <t xml:space="preserve">Map decision, debtToIncomePercent, maxAllowedPercent, referenceId to JSON; derive eligible; response per SDD 4.3. AC: clean JSON, no XML.</t>
   </si>
   <si>
     <t xml:space="preserve">S6.4</t>
@@ -663,7 +705,7 @@
     <t xml:space="preserve">SOAP fault and transport error mapping</t>
   </si>
   <si>
-    <t xml:space="preserve">Divide-by-zero fault -&gt; 422 ELIGIBILITY_REJECTED; other faults -&gt; 502; 10 s timeout -&gt; 504; unreachable -&gt; 503. AC: no SOAP XML ever reaches the client.</t>
+    <t xml:space="preserve">soap:Client (INVALID_INCOME, CUSTOMER_BLACKLISTED) -&gt; 422 ELIGIBILITY_REJECTED; soap:Server -&gt; 502; 10 s timeout -&gt; 504; unreachable -&gt; 503. AC: no SOAP XML ever reaches the client.</t>
   </si>
   <si>
     <t xml:space="preserve">S6.5</t>
@@ -672,7 +714,7 @@
     <t xml:space="preserve">Loan API tests</t>
   </si>
   <si>
-    <t xml:space="preserve">MI unit test suite with a mock service returning DivideResult and SOAP faults; WireMock delay for 504. AC: 200, 400, 422, 502, 504 proven.</t>
+    <t xml:space="preserve">MI unit test suite with a mock service returning CheckEligibilityResponse and Client/Server faults; mock backends rule 5004 (12 s) for 504. AC: 200, 400, 422, 502, 504 proven.</t>
   </si>
   <si>
     <t xml:space="preserve">S6.6</t>
@@ -780,7 +822,7 @@
     <t xml:space="preserve">Jenkins credentials and job</t>
   </si>
   <si>
-    <t xml:space="preserve">APIM admin, DB, registry credentials; pipeline job from Git; dist volume mounted. AC: job checks out repo.</t>
+    <t xml:space="preserve">APIM admin, DB, registry credentials; pipeline job from Git; dist volume mounted; mock backends running on jamii-shared before tests. AC: job checks out repo.</t>
   </si>
   <si>
     <t xml:space="preserve">S10.3</t>
@@ -888,7 +930,7 @@
     <t xml:space="preserve">Fault drills</t>
   </si>
   <si>
-    <t xml:space="preserve">Stop H2 -&gt; 503; WireMock delay -&gt; 504; SOAP fault -&gt; 422. AC: all observed and recorded.</t>
+    <t xml:space="preserve">Stop H2 -&gt; 503; mock rules 5004 -&gt; 504; credit 6000 / income 0 -&gt; 422; 5000 -&gt; 502; stop mock backends -&gt; 503. AC: all observed and recorded.</t>
   </si>
   <si>
     <t xml:space="preserve">S11.5</t>
@@ -1603,7 +1645,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -1694,7 +1736,7 @@
       </c>
       <c r="C4" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A4,'Jira Import'!$B:$B,"Story")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A4,'Jira Import'!$B:$B,"Sub-task")</f>
@@ -1702,11 +1744,11 @@
       </c>
       <c r="E4" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$H:$H,'Jira Import'!$O:$O,A4)</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F4" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$I:$I,'Jira Import'!$O:$O,A4,'Jira Import'!$B:$B,"Story")</f>
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="G4" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A4,'Jira Import'!$N:$N,"Done",'Jira Import'!$B:$B,"Story")</f>
@@ -1758,7 +1800,7 @@
       </c>
       <c r="C6" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A6,'Jira Import'!$B:$B,"Story")</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A6,'Jira Import'!$B:$B,"Sub-task")</f>
@@ -1766,11 +1808,11 @@
       </c>
       <c r="E6" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$H:$H,'Jira Import'!$O:$O,A6)</f>
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$I:$I,'Jira Import'!$O:$O,A6,'Jira Import'!$B:$B,"Story")</f>
-        <v>7</v>
+        <v>2.75</v>
       </c>
       <c r="G6" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A6,'Jira Import'!$N:$N,"Done",'Jira Import'!$B:$B,"Story")</f>
@@ -1778,7 +1820,7 @@
       </c>
       <c r="H6" s="4" t="n">
         <f aca="false">IF(INDEX('Jira Import'!$L:$L,MATCH(A6,'Jira Import'!$A:$A,0))="","",INDEX('Jira Import'!$L:$L,MATCH(A6,'Jira Import'!$A:$A,0)))</f>
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1790,7 +1832,7 @@
       </c>
       <c r="C7" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A7,'Jira Import'!$B:$B,"Story")</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D7" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A7,'Jira Import'!$B:$B,"Sub-task")</f>
@@ -1798,11 +1840,11 @@
       </c>
       <c r="E7" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$H:$H,'Jira Import'!$O:$O,A7)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F7" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$I:$I,'Jira Import'!$O:$O,A7,'Jira Import'!$B:$B,"Story")</f>
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="G7" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A7,'Jira Import'!$N:$N,"Done",'Jira Import'!$B:$B,"Story")</f>
@@ -1830,11 +1872,11 @@
       </c>
       <c r="E8" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$H:$H,'Jira Import'!$O:$O,A8)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$I:$I,'Jira Import'!$O:$O,A8,'Jira Import'!$B:$B,"Story")</f>
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G8" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A8,'Jira Import'!$N:$N,"Done",'Jira Import'!$B:$B,"Story")</f>
@@ -1854,7 +1896,7 @@
       </c>
       <c r="C9" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A9,'Jira Import'!$B:$B,"Story")</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D9" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A9,'Jira Import'!$B:$B,"Sub-task")</f>
@@ -1862,11 +1904,11 @@
       </c>
       <c r="E9" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$H:$H,'Jira Import'!$O:$O,A9)</f>
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F9" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$I:$I,'Jira Import'!$O:$O,A9,'Jira Import'!$B:$B,"Story")</f>
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="G9" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A9,'Jira Import'!$N:$N,"Done",'Jira Import'!$B:$B,"Story")</f>
@@ -1886,7 +1928,7 @@
       </c>
       <c r="C10" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A10,'Jira Import'!$B:$B,"Story")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A10,'Jira Import'!$B:$B,"Sub-task")</f>
@@ -1894,11 +1936,11 @@
       </c>
       <c r="E10" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$H:$H,'Jira Import'!$O:$O,A10)</f>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F10" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$I:$I,'Jira Import'!$O:$O,A10,'Jira Import'!$B:$B,"Story")</f>
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="G10" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A10,'Jira Import'!$N:$N,"Done",'Jira Import'!$B:$B,"Story")</f>
@@ -1906,7 +1948,7 @@
       </c>
       <c r="H10" s="4" t="n">
         <f aca="false">IF(INDEX('Jira Import'!$L:$L,MATCH(A10,'Jira Import'!$A:$A,0))="","",INDEX('Jira Import'!$L:$L,MATCH(A10,'Jira Import'!$A:$A,0)))</f>
-        <v>46306</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1918,7 +1960,7 @@
       </c>
       <c r="C11" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A11,'Jira Import'!$B:$B,"Story")</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D11" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A11,'Jira Import'!$B:$B,"Sub-task")</f>
@@ -1926,11 +1968,11 @@
       </c>
       <c r="E11" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$H:$H,'Jira Import'!$O:$O,A11)</f>
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F11" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$I:$I,'Jira Import'!$O:$O,A11,'Jira Import'!$B:$B,"Story")</f>
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="G11" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A11,'Jira Import'!$N:$N,"Done",'Jira Import'!$B:$B,"Story")</f>
@@ -1938,7 +1980,7 @@
       </c>
       <c r="H11" s="4" t="n">
         <f aca="false">IF(INDEX('Jira Import'!$L:$L,MATCH(A11,'Jira Import'!$A:$A,0))="","",INDEX('Jira Import'!$L:$L,MATCH(A11,'Jira Import'!$A:$A,0)))</f>
-        <v>46307</v>
+        <v>46306</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1950,7 +1992,7 @@
       </c>
       <c r="C12" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A12,'Jira Import'!$B:$B,"Story")</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A12,'Jira Import'!$B:$B,"Sub-task")</f>
@@ -1958,11 +2000,11 @@
       </c>
       <c r="E12" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$H:$H,'Jira Import'!$O:$O,A12)</f>
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F12" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$I:$I,'Jira Import'!$O:$O,A12,'Jira Import'!$B:$B,"Story")</f>
-        <v>3.5</v>
+        <v>10.5</v>
       </c>
       <c r="G12" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A12,'Jira Import'!$N:$N,"Done",'Jira Import'!$B:$B,"Story")</f>
@@ -1990,19 +2032,19 @@
       </c>
       <c r="E13" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$H:$H,'Jira Import'!$O:$O,A13)</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F13" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$I:$I,'Jira Import'!$O:$O,A13,'Jira Import'!$B:$B,"Story")</f>
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="G13" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A13,'Jira Import'!$N:$N,"Done",'Jira Import'!$B:$B,"Story")</f>
         <v>0</v>
       </c>
-      <c r="H13" s="4" t="str">
+      <c r="H13" s="4" t="n">
         <f aca="false">IF(INDEX('Jira Import'!$L:$L,MATCH(A13,'Jira Import'!$A:$A,0))="","",INDEX('Jira Import'!$L:$L,MATCH(A13,'Jira Import'!$A:$A,0)))</f>
-        <v/>
+        <v>46307</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2014,7 +2056,7 @@
       </c>
       <c r="C14" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A14,'Jira Import'!$B:$B,"Story")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A14,'Jira Import'!$B:$B,"Sub-task")</f>
@@ -2022,19 +2064,19 @@
       </c>
       <c r="E14" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$H:$H,'Jira Import'!$O:$O,A14)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F14" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$I:$I,'Jira Import'!$O:$O,A14,'Jira Import'!$B:$B,"Story")</f>
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G14" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A14,'Jira Import'!$N:$N,"Done",'Jira Import'!$B:$B,"Story")</f>
         <v>0</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="4" t="str">
         <f aca="false">IF(INDEX('Jira Import'!$L:$L,MATCH(A14,'Jira Import'!$A:$A,0))="","",INDEX('Jira Import'!$L:$L,MATCH(A14,'Jira Import'!$A:$A,0)))</f>
-        <v>46307</v>
+        <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2046,7 +2088,7 @@
       </c>
       <c r="C15" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A15,'Jira Import'!$B:$B,"Story")</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D15" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A15,'Jira Import'!$B:$B,"Sub-task")</f>
@@ -2054,7 +2096,7 @@
       </c>
       <c r="E15" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$H:$H,'Jira Import'!$O:$O,A15)</f>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F15" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$I:$I,'Jira Import'!$O:$O,A15,'Jira Import'!$B:$B,"Story")</f>
@@ -2064,52 +2106,74 @@
         <f aca="false">COUNTIFS('Jira Import'!$O:$O,A15,'Jira Import'!$N:$N,"Done",'Jira Import'!$B:$B,"Story")</f>
         <v>0</v>
       </c>
-      <c r="H15" s="4" t="str">
+      <c r="H15" s="4" t="n">
         <f aca="false">IF(INDEX('Jira Import'!$L:$L,MATCH(A15,'Jira Import'!$A:$A,0))="","",INDEX('Jira Import'!$L:$L,MATCH(A15,'Jira Import'!$A:$A,0)))</f>
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <f aca="false">COUNTIFS('Jira Import'!$O:$O,A16,'Jira Import'!$B:$B,"Story")</f>
+        <v>2</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <f aca="false">COUNTIFS('Jira Import'!$O:$O,A16,'Jira Import'!$B:$B,"Sub-task")</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <f aca="false">SUMIFS('Jira Import'!$H:$H,'Jira Import'!$O:$O,A16)</f>
+        <v>13</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <f aca="false">SUMIFS('Jira Import'!$I:$I,'Jira Import'!$O:$O,A16,'Jira Import'!$B:$B,"Story")</f>
+        <v>7</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <f aca="false">COUNTIFS('Jira Import'!$O:$O,A16,'Jira Import'!$N:$N,"Done",'Jira Import'!$B:$B,"Story")</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="4" t="str">
+        <f aca="false">IF(INDEX('Jira Import'!$L:$L,MATCH(A16,'Jira Import'!$A:$A,0))="","",INDEX('Jira Import'!$L:$L,MATCH(A16,'Jira Import'!$A:$A,0)))</f>
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5" t="n">
-        <f aca="false">SUM(C3:C15)</f>
-        <v>73</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <f aca="false">SUM(D3:D15)</f>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5" t="n">
+        <f aca="false">SUM(C3:C16)</f>
+        <v>76</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <f aca="false">SUM(D3:D16)</f>
         <v>3</v>
       </c>
-      <c r="E16" s="5" t="n">
-        <f aca="false">SUM(E3:E15)</f>
-        <v>162</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <f aca="false">SUM(F3:F15)</f>
-        <v>90</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <f aca="false">SUM(G3:G15)</f>
+      <c r="E17" s="5" t="n">
+        <f aca="false">SUM(E3:E16)</f>
+        <v>165</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <f aca="false">SUM(F3:F16)</f>
+        <v>90.75</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <f aca="false">SUM(G3:G16)</f>
         <v>3</v>
       </c>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
+      <c r="H17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -2118,10 +2182,8 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
     </row>
-    <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>37</v>
-      </c>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -2130,70 +2192,57 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="3" t="s">
+    <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>42</v>
-      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="4" t="n">
-        <v>46302</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <f aca="false">COUNTIFS('Jira Import'!$L:$L,B21,'Jira Import'!$B:$B,"Story")</f>
-        <v>6</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <f aca="false">SUMIFS('Jira Import'!$I:$I,'Jira Import'!$L:$L,B21,'Jira Import'!$B:$B,"Story")</f>
-        <v>11</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <f aca="false">D21-E21</f>
-        <v>0</v>
+      <c r="F21" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B22" s="4" t="n">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="C22" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$L:$L,B22,'Jira Import'!$B:$B,"Story")</f>
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D22" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$I:$I,'Jira Import'!$L:$L,B22,'Jira Import'!$B:$B,"Story")</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F22" s="2" t="n">
         <f aca="false">D22-E22</f>
@@ -2204,64 +2253,64 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B23" s="4" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="C23" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$L:$L,B23,'Jira Import'!$B:$B,"Story")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D23" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$I:$I,'Jira Import'!$L:$L,B23,'Jira Import'!$B:$B,"Story")</f>
-        <v>12.5</v>
+        <v>12.75</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>13</v>
       </c>
       <c r="F23" s="2" t="n">
         <f aca="false">D23-E23</f>
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B24" s="4" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="C24" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$L:$L,B24,'Jira Import'!$B:$B,"Story")</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D24" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$I:$I,'Jira Import'!$L:$L,B24,'Jira Import'!$B:$B,"Story")</f>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>13</v>
       </c>
       <c r="F24" s="2" t="n">
         <f aca="false">D24-E24</f>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B25" s="4" t="n">
-        <v>46306</v>
+        <v>46305</v>
       </c>
       <c r="C25" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$L:$L,B25,'Jira Import'!$B:$B,"Story")</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$I:$I,'Jira Import'!$L:$L,B25,'Jira Import'!$B:$B,"Story")</f>
@@ -2279,10 +2328,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B26" s="4" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="C26" s="2" t="n">
         <f aca="false">COUNTIFS('Jira Import'!$L:$L,B26,'Jira Import'!$B:$B,"Story")</f>
@@ -2290,29 +2339,54 @@
       </c>
       <c r="D26" s="2" t="n">
         <f aca="false">SUMIFS('Jira Import'!$I:$I,'Jira Import'!$L:$L,B26,'Jira Import'!$B:$B,"Story")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>13</v>
       </c>
       <c r="F26" s="2" t="n">
         <f aca="false">D26-E26</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
+      <c r="A27" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <f aca="false">COUNTIFS('Jira Import'!$L:$L,B27,'Jira Import'!$B:$B,"Story")</f>
+        <v>12</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <f aca="false">SUMIFS('Jira Import'!$I:$I,'Jira Import'!$L:$L,B27,'Jira Import'!$B:$B,"Story")</f>
+        <v>12</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <f aca="false">D27-E27</f>
+        <v>-1</v>
+      </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2330,7 +2404,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O90"/>
+  <dimension ref="A1:O94"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -2349,49 +2423,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2405,14 +2479,14 @@
         <v>10</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -2427,10 +2501,10 @@
         <v>46302</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O2" s="9" t="s">
         <v>9</v>
@@ -2438,25 +2512,25 @@
     </row>
     <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H3" s="12" t="n">
         <v>3</v>
@@ -2475,10 +2549,10 @@
         <v>46302</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N3" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O3" s="12" t="s">
         <v>9</v>
@@ -2486,25 +2560,25 @@
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H4" s="12" t="n">
         <v>5</v>
@@ -2523,10 +2597,10 @@
         <v>46302</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O4" s="12" t="s">
         <v>9</v>
@@ -2534,25 +2608,25 @@
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H5" s="12" t="n">
         <v>1</v>
@@ -2571,10 +2645,10 @@
         <v>46302</v>
       </c>
       <c r="M5" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N5" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O5" s="12" t="s">
         <v>9</v>
@@ -2582,25 +2656,25 @@
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>1</v>
@@ -2619,10 +2693,10 @@
         <v>46302</v>
       </c>
       <c r="M6" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O6" s="12" t="s">
         <v>9</v>
@@ -2639,14 +2713,14 @@
         <v>12</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
@@ -2661,10 +2735,10 @@
         <v>46303</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O7" s="9" t="s">
         <v>11</v>
@@ -2672,25 +2746,25 @@
     </row>
     <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>2</v>
@@ -2709,10 +2783,10 @@
         <v>46302</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O8" s="12" t="s">
         <v>11</v>
@@ -2720,25 +2794,25 @@
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E9" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="15" t="s">
         <v>88</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>86</v>
       </c>
       <c r="H9" s="15"/>
       <c r="I9" s="15" t="n">
@@ -2755,10 +2829,10 @@
         <v>46302</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O9" s="15" t="s">
         <v>11</v>
@@ -2766,25 +2840,25 @@
     </row>
     <row r="10" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H10" s="12" t="n">
         <v>1</v>
@@ -2803,10 +2877,10 @@
         <v>46302</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N10" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O10" s="12" t="s">
         <v>11</v>
@@ -2814,25 +2888,25 @@
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>1</v>
@@ -2851,10 +2925,10 @@
         <v>46303</v>
       </c>
       <c r="M11" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O11" s="12" t="s">
         <v>11</v>
@@ -2862,25 +2936,25 @@
     </row>
     <row r="12" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>3</v>
@@ -2899,10 +2973,10 @@
         <v>46303</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O12" s="12" t="s">
         <v>11</v>
@@ -2910,25 +2984,25 @@
     </row>
     <row r="13" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>5</v>
@@ -2947,10 +3021,10 @@
         <v>46303</v>
       </c>
       <c r="M13" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O13" s="12" t="s">
         <v>11</v>
@@ -2958,25 +3032,25 @@
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H14" s="15"/>
       <c r="I14" s="15" t="n">
@@ -2993,10 +3067,10 @@
         <v>46303</v>
       </c>
       <c r="M14" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N14" s="15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O14" s="15" t="s">
         <v>11</v>
@@ -3004,25 +3078,25 @@
     </row>
     <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H15" s="15"/>
       <c r="I15" s="15" t="n">
@@ -3039,10 +3113,10 @@
         <v>46303</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N15" s="15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O15" s="15" t="s">
         <v>11</v>
@@ -3050,25 +3124,25 @@
     </row>
     <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E16" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>1</v>
@@ -3087,10 +3161,10 @@
         <v>46303</v>
       </c>
       <c r="M16" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O16" s="12" t="s">
         <v>11</v>
@@ -3098,25 +3172,25 @@
     </row>
     <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>2</v>
@@ -3135,10 +3209,10 @@
         <v>46303</v>
       </c>
       <c r="M17" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O17" s="12" t="s">
         <v>11</v>
@@ -3146,35 +3220,35 @@
     </row>
     <row r="18" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J18" s="12" t="n">
         <f aca="false">IF(I18="","",I18*3600)</f>
-        <v>3600</v>
+        <v>5400</v>
       </c>
       <c r="K18" s="14" t="n">
         <v>46303</v>
@@ -3183,10 +3257,10 @@
         <v>46303</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O18" s="12" t="s">
         <v>11</v>
@@ -3194,35 +3268,35 @@
     </row>
     <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J19" s="12" t="n">
         <f aca="false">IF(I19="","",I19*3600)</f>
-        <v>5400</v>
+        <v>1800</v>
       </c>
       <c r="K19" s="14" t="n">
         <v>46303</v>
@@ -3231,340 +3305,340 @@
         <v>46303</v>
       </c>
       <c r="M19" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O19" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="D20" s="13" t="s">
+    <row r="20" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="E20" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J20" s="12" t="n">
+      <c r="E20" s="9"/>
+      <c r="F20" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9" t="str">
         <f aca="false">IF(I20="","",I20*3600)</f>
-        <v>1800</v>
-      </c>
-      <c r="K20" s="14" t="n">
-        <v>46303</v>
-      </c>
-      <c r="L20" s="14" t="n">
-        <v>46303</v>
-      </c>
-      <c r="M20" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="N20" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="O20" s="12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
+        <v/>
+      </c>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="O20" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="10" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9" t="s">
+      <c r="G21" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="H21" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <f aca="false">IF(I21="","",I21*3600)</f>
+        <v>5400</v>
+      </c>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9" t="str">
-        <f aca="false">IF(I21="","",I21*3600)</f>
-        <v/>
-      </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="N21" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="O21" s="9" t="s">
+      <c r="N21" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="O21" s="12" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>13</v>
       </c>
       <c r="F22" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G22" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="G22" s="12" t="s">
-        <v>130</v>
-      </c>
       <c r="H22" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J22" s="12" t="n">
         <f aca="false">IF(I22="","",I22*3600)</f>
-        <v>5400</v>
+        <v>1800</v>
       </c>
       <c r="K22" s="14"/>
       <c r="L22" s="14"/>
       <c r="M22" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O22" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>13</v>
       </c>
       <c r="F23" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G23" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="G23" s="12" t="s">
-        <v>130</v>
-      </c>
       <c r="H23" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="I23" s="12" t="n">
-        <v>0.5</v>
       </c>
       <c r="J23" s="12" t="n">
         <f aca="false">IF(I23="","",I23*3600)</f>
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="K23" s="14"/>
       <c r="L23" s="14"/>
       <c r="M23" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O23" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>13</v>
       </c>
       <c r="F24" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>130</v>
-      </c>
       <c r="H24" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J24" s="12" t="n">
         <f aca="false">IF(I24="","",I24*3600)</f>
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
       <c r="M24" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O24" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="D25" s="13" t="s">
+    <row r="25" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="E25" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="H25" s="12" t="n">
+      <c r="E25" s="9"/>
+      <c r="F25" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9" t="str">
+        <f aca="false">IF(I25="","",I25*3600)</f>
+        <v/>
+      </c>
+      <c r="K25" s="11" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L25" s="11" t="n">
+        <v>46303</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="H26" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <f aca="false">IF(I25="","",I25*3600)</f>
-        <v>1800</v>
-      </c>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="N25" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="O25" s="12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
+      <c r="I26" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J26" s="12" t="n">
+        <f aca="false">IF(I26="","",I26*3600)</f>
+        <v>900</v>
+      </c>
+      <c r="K26" s="14" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L26" s="14" t="n">
+        <v>46303</v>
+      </c>
+      <c r="M26" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="O26" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9" t="str">
-        <f aca="false">IF(I26="","",I26*3600)</f>
-        <v/>
-      </c>
-      <c r="K26" s="11" t="n">
-        <v>46303</v>
-      </c>
-      <c r="L26" s="11" t="n">
-        <v>46304</v>
-      </c>
-      <c r="M26" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="N26" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="O26" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="27" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E27" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>2</v>
@@ -3583,46 +3657,46 @@
         <v>46303</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O27" s="12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="J28" s="12" t="n">
         <f aca="false">IF(I28="","",I28*3600)</f>
-        <v>1800</v>
+        <v>2700</v>
       </c>
       <c r="K28" s="14" t="n">
         <v>46303</v>
@@ -3631,10 +3705,10 @@
         <v>46303</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O28" s="12" t="s">
         <v>15</v>
@@ -3642,35 +3716,35 @@
     </row>
     <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E29" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J29" s="12" t="n">
         <f aca="false">IF(I29="","",I29*3600)</f>
-        <v>5400</v>
+        <v>1800</v>
       </c>
       <c r="K29" s="14" t="n">
         <v>46303</v>
@@ -3679,180 +3753,174 @@
         <v>46303</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O29" s="12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="J30" s="12" t="n">
         <f aca="false">IF(I30="","",I30*3600)</f>
-        <v>3600</v>
+        <v>900</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="L30" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O30" s="12" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="D31" s="13" t="s">
+      <c r="A31" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="E31" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="H31" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="12" t="n">
+      <c r="E31" s="9"/>
+      <c r="F31" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9" t="str">
         <f aca="false">IF(I31="","",I31*3600)</f>
-        <v>3600</v>
-      </c>
-      <c r="K31" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K31" s="11" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L31" s="11" t="n">
         <v>46304</v>
       </c>
-      <c r="L31" s="14" t="n">
-        <v>46304</v>
-      </c>
-      <c r="M31" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="N31" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="O31" s="12" t="s">
-        <v>15</v>
+      <c r="M31" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="N31" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G32" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G32" s="12" t="s">
-        <v>145</v>
-      </c>
       <c r="H32" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J32" s="12" t="n">
         <f aca="false">IF(I32="","",I32*3600)</f>
-        <v>5400</v>
+        <v>3600</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="L32" s="14" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="M32" s="12" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O32" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>1</v>
@@ -3871,88 +3939,94 @@
         <v>46304</v>
       </c>
       <c r="M33" s="12" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O33" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="E34" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B34" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9" t="str">
+      <c r="F34" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J34" s="12" t="n">
         <f aca="false">IF(I34="","",I34*3600)</f>
-        <v/>
-      </c>
-      <c r="K34" s="11" t="n">
+        <v>5400</v>
+      </c>
+      <c r="K34" s="14" t="n">
         <v>46304</v>
       </c>
-      <c r="L34" s="11" t="n">
+      <c r="L34" s="14" t="n">
         <v>46304</v>
       </c>
-      <c r="M34" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="N34" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="O34" s="9" t="s">
+      <c r="M34" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="N34" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="O34" s="12" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E35" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="H35" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="I35" s="12" t="n">
-        <v>0.5</v>
       </c>
       <c r="J35" s="12" t="n">
         <f aca="false">IF(I35="","",I35*3600)</f>
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="K35" s="14" t="n">
         <v>46304</v>
@@ -3961,36 +4035,36 @@
         <v>46304</v>
       </c>
       <c r="M35" s="12" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O35" s="12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E36" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>2</v>
@@ -4009,46 +4083,46 @@
         <v>46304</v>
       </c>
       <c r="M36" s="12" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O36" s="12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E37" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J37" s="12" t="n">
         <f aca="false">IF(I37="","",I37*3600)</f>
-        <v>7200</v>
+        <v>5400</v>
       </c>
       <c r="K37" s="14" t="n">
         <v>46304</v>
@@ -4057,10 +4131,10 @@
         <v>46304</v>
       </c>
       <c r="M37" s="12" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="N37" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O37" s="12" t="s">
         <v>17</v>
@@ -4068,35 +4142,35 @@
     </row>
     <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J38" s="12" t="n">
         <f aca="false">IF(I38="","",I38*3600)</f>
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="K38" s="14" t="n">
         <v>46304</v>
@@ -4105,10 +4179,10 @@
         <v>46304</v>
       </c>
       <c r="M38" s="12" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="N38" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O38" s="12" t="s">
         <v>17</v>
@@ -4125,14 +4199,14 @@
         <v>20</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
@@ -4147,10 +4221,10 @@
         <v>46304</v>
       </c>
       <c r="M39" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>19</v>
@@ -4158,25 +4232,25 @@
     </row>
     <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>19</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>1</v>
@@ -4195,46 +4269,46 @@
         <v>46304</v>
       </c>
       <c r="M40" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N40" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O40" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E41" s="12" t="s">
         <v>19</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H41" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="I41" s="12" t="n">
-        <v>0.5</v>
       </c>
       <c r="J41" s="12" t="n">
         <f aca="false">IF(I41="","",I41*3600)</f>
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="K41" s="14" t="n">
         <v>46304</v>
@@ -4243,10 +4317,10 @@
         <v>46304</v>
       </c>
       <c r="M41" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N41" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O41" s="12" t="s">
         <v>19</v>
@@ -4254,25 +4328,25 @@
     </row>
     <row r="42" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E42" s="12" t="s">
         <v>19</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>3</v>
@@ -4291,10 +4365,10 @@
         <v>46304</v>
       </c>
       <c r="M42" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N42" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O42" s="12" t="s">
         <v>19</v>
@@ -4302,25 +4376,25 @@
     </row>
     <row r="43" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E43" s="12" t="s">
         <v>19</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H43" s="12" t="n">
         <v>2</v>
@@ -4339,16 +4413,16 @@
         <v>46304</v>
       </c>
       <c r="M43" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N43" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O43" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
         <v>21</v>
       </c>
@@ -4359,14 +4433,14 @@
         <v>22</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E44" s="9"/>
       <c r="F44" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
@@ -4375,138 +4449,138 @@
         <v/>
       </c>
       <c r="K44" s="11" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="L44" s="11" t="n">
         <v>46305</v>
       </c>
       <c r="M44" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N44" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O44" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E45" s="12" t="s">
         <v>21</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J45" s="12" t="n">
         <f aca="false">IF(I45="","",I45*3600)</f>
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="K45" s="14" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="L45" s="14" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="M45" s="12" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N45" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O45" s="12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>21</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J46" s="12" t="n">
         <f aca="false">IF(I46="","",I46*3600)</f>
-        <v>5400</v>
+        <v>7200</v>
       </c>
       <c r="K46" s="14" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="L46" s="14" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="M46" s="12" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N46" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O46" s="12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E47" s="12" t="s">
         <v>21</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H47" s="12" t="n">
         <v>2</v>
@@ -4525,84 +4599,78 @@
         <v>46305</v>
       </c>
       <c r="M47" s="12" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N47" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O47" s="12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="D48" s="13" t="s">
+    <row r="48" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="E48" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G48" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="H48" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I48" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J48" s="12" t="n">
+      <c r="E48" s="9"/>
+      <c r="F48" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9" t="str">
         <f aca="false">IF(I48="","",I48*3600)</f>
-        <v>5400</v>
-      </c>
-      <c r="K48" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K48" s="11" t="n">
         <v>46305</v>
       </c>
-      <c r="L48" s="14" t="n">
+      <c r="L48" s="11" t="n">
         <v>46305</v>
       </c>
-      <c r="M48" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="N48" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="O48" s="12" t="s">
-        <v>21</v>
+      <c r="M48" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="N48" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="O48" s="9" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G49" s="12" t="s">
         <v>213</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F49" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="G49" s="12" t="s">
-        <v>199</v>
       </c>
       <c r="H49" s="12" t="n">
         <v>2</v>
@@ -4621,36 +4689,36 @@
         <v>46305</v>
       </c>
       <c r="M49" s="12" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="N49" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O49" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>2</v>
@@ -4669,88 +4737,94 @@
         <v>46305</v>
       </c>
       <c r="M50" s="12" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="N50" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O50" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="9" t="s">
+      <c r="A51" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="E51" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="F51" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="H51" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C51" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="H51" s="9"/>
-      <c r="I51" s="9"/>
-      <c r="J51" s="9" t="str">
+      <c r="I51" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="12" t="n">
         <f aca="false">IF(I51="","",I51*3600)</f>
-        <v/>
-      </c>
-      <c r="K51" s="11" t="n">
+        <v>3600</v>
+      </c>
+      <c r="K51" s="14" t="n">
         <v>46305</v>
       </c>
-      <c r="L51" s="11" t="n">
-        <v>46306</v>
-      </c>
-      <c r="M51" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="N51" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="O51" s="9" t="s">
+      <c r="L51" s="14" t="n">
+        <v>46305</v>
+      </c>
+      <c r="M51" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="N51" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="O51" s="12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E52" s="12" t="s">
         <v>23</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J52" s="12" t="n">
         <f aca="false">IF(I52="","",I52*3600)</f>
-        <v>7200</v>
+        <v>5400</v>
       </c>
       <c r="K52" s="14" t="n">
         <v>46305</v>
@@ -4759,46 +4833,46 @@
         <v>46305</v>
       </c>
       <c r="M52" s="12" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="N52" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O52" s="12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E53" s="12" t="s">
         <v>23</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G53" s="12" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="H53" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="I53" s="12" t="n">
-        <v>0.5</v>
       </c>
       <c r="J53" s="12" t="n">
         <f aca="false">IF(I53="","",I53*3600)</f>
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="K53" s="14" t="n">
         <v>46305</v>
@@ -4807,46 +4881,46 @@
         <v>46305</v>
       </c>
       <c r="M53" s="12" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="N53" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O53" s="12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>23</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G54" s="12" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J54" s="12" t="n">
         <f aca="false">IF(I54="","",I54*3600)</f>
-        <v>10800</v>
+        <v>3600</v>
       </c>
       <c r="K54" s="14" t="n">
         <v>46305</v>
@@ -4855,270 +4929,270 @@
         <v>46305</v>
       </c>
       <c r="M54" s="12" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="N54" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O54" s="12" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="D55" s="13" t="s">
+      <c r="A55" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D55" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="E55" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F55" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G55" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="H55" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I55" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J55" s="12" t="n">
+      <c r="E55" s="9"/>
+      <c r="F55" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9" t="str">
         <f aca="false">IF(I55="","",I55*3600)</f>
-        <v>5400</v>
-      </c>
-      <c r="K55" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K55" s="11" t="n">
+        <v>46305</v>
+      </c>
+      <c r="L55" s="11" t="n">
         <v>46306</v>
       </c>
-      <c r="L55" s="14" t="n">
-        <v>46306</v>
-      </c>
-      <c r="M55" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="N55" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="O55" s="12" t="s">
-        <v>23</v>
+      <c r="M55" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="N55" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="O55" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G56" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="B56" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="D56" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F56" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G56" s="12" t="s">
-        <v>220</v>
-      </c>
       <c r="H56" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I56" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="I56" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="J56" s="12" t="n">
         <f aca="false">IF(I56="","",I56*3600)</f>
-        <v>3600</v>
+        <v>7200</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>46306</v>
+        <v>46305</v>
       </c>
       <c r="L56" s="14" t="n">
-        <v>46306</v>
+        <v>46305</v>
       </c>
       <c r="M56" s="12" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="N56" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O56" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J57" s="12" t="n">
         <f aca="false">IF(I57="","",I57*3600)</f>
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="K57" s="14" t="n">
-        <v>46306</v>
+        <v>46305</v>
       </c>
       <c r="L57" s="14" t="n">
-        <v>46306</v>
+        <v>46305</v>
       </c>
       <c r="M57" s="12" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="N57" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O57" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G58" s="12" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J58" s="12" t="n">
         <f aca="false">IF(I58="","",I58*3600)</f>
-        <v>1800</v>
+        <v>10800</v>
       </c>
       <c r="K58" s="14" t="n">
+        <v>46305</v>
+      </c>
+      <c r="L58" s="14" t="n">
+        <v>46305</v>
+      </c>
+      <c r="M58" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="N58" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="O58" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G59" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="H59" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I59" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J59" s="12" t="n">
+        <f aca="false">IF(I59="","",I59*3600)</f>
+        <v>5400</v>
+      </c>
+      <c r="K59" s="14" t="n">
         <v>46306</v>
       </c>
-      <c r="L58" s="14" t="n">
+      <c r="L59" s="14" t="n">
         <v>46306</v>
       </c>
-      <c r="M58" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="N58" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="O58" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D59" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G59" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="H59" s="9"/>
-      <c r="I59" s="9"/>
-      <c r="J59" s="9" t="str">
-        <f aca="false">IF(I59="","",I59*3600)</f>
-        <v/>
-      </c>
-      <c r="K59" s="11" t="n">
-        <v>46306</v>
-      </c>
-      <c r="L59" s="11" t="n">
-        <v>46307</v>
-      </c>
-      <c r="M59" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="N59" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="O59" s="9" t="s">
+      <c r="M59" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="N59" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="O59" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E60" s="12" t="s">
         <v>25</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="H60" s="12" t="n">
         <v>2</v>
@@ -5137,46 +5211,46 @@
         <v>46306</v>
       </c>
       <c r="M60" s="12" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="N60" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O60" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E61" s="12" t="s">
         <v>25</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G61" s="12" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="H61" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I61" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="I61" s="12" t="n">
-        <v>0.5</v>
       </c>
       <c r="J61" s="12" t="n">
         <f aca="false">IF(I61="","",I61*3600)</f>
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="K61" s="14" t="n">
         <v>46306</v>
@@ -5185,10 +5259,10 @@
         <v>46306</v>
       </c>
       <c r="M61" s="12" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="N61" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O61" s="12" t="s">
         <v>25</v>
@@ -5196,35 +5270,35 @@
     </row>
     <row r="62" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E62" s="12" t="s">
         <v>25</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G62" s="12" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J62" s="12" t="n">
         <f aca="false">IF(I62="","",I62*3600)</f>
-        <v>9000</v>
+        <v>1800</v>
       </c>
       <c r="K62" s="14" t="n">
         <v>46306</v>
@@ -5233,94 +5307,88 @@
         <v>46306</v>
       </c>
       <c r="M62" s="12" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="N62" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O62" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="B63" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C63" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="D63" s="13" t="s">
+      <c r="A63" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D63" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="E63" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F63" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G63" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="H63" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I63" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="12" t="n">
+      <c r="E63" s="9"/>
+      <c r="F63" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H63" s="9"/>
+      <c r="I63" s="9"/>
+      <c r="J63" s="9" t="str">
         <f aca="false">IF(I63="","",I63*3600)</f>
-        <v>3600</v>
-      </c>
-      <c r="K63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K63" s="11" t="n">
         <v>46306</v>
       </c>
-      <c r="L63" s="14" t="n">
-        <v>46306</v>
-      </c>
-      <c r="M63" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="N63" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="O63" s="12" t="s">
-        <v>25</v>
+      <c r="L63" s="11" t="n">
+        <v>46307</v>
+      </c>
+      <c r="M63" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="N63" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="O63" s="9" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G64" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="B64" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C64" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="E64" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F64" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G64" s="12" t="s">
-        <v>244</v>
-      </c>
       <c r="H64" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J64" s="12" t="n">
         <f aca="false">IF(I64="","",I64*3600)</f>
-        <v>7200</v>
+        <v>3600</v>
       </c>
       <c r="K64" s="14" t="n">
         <v>46306</v>
@@ -5329,46 +5397,46 @@
         <v>46306</v>
       </c>
       <c r="M64" s="12" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="N64" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O64" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J65" s="12" t="n">
         <f aca="false">IF(I65="","",I65*3600)</f>
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="K65" s="14" t="n">
         <v>46306</v>
@@ -5377,244 +5445,250 @@
         <v>46306</v>
       </c>
       <c r="M65" s="12" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="N65" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O65" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G66" s="12" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J66" s="12" t="n">
         <f aca="false">IF(I66="","",I66*3600)</f>
-        <v>5400</v>
+        <v>9000</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="L66" s="14" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="M66" s="12" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="N66" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O66" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="12" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G67" s="12" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="H67" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I67" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="I67" s="12" t="n">
-        <v>0.5</v>
       </c>
       <c r="J67" s="12" t="n">
         <f aca="false">IF(I67="","",I67*3600)</f>
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="K67" s="14" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="L67" s="14" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="M67" s="12" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="N67" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O67" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J68" s="12" t="n">
         <f aca="false">IF(I68="","",I68*3600)</f>
-        <v>1800</v>
+        <v>7200</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="L68" s="14" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="M68" s="12" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="N68" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O68" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B69" s="9" t="s">
+    </row>
+    <row r="69" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="B69" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G69" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H69" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C69" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D69" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="H69" s="9"/>
-      <c r="I69" s="9"/>
-      <c r="J69" s="9" t="str">
+      <c r="I69" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" s="12" t="n">
         <f aca="false">IF(I69="","",I69*3600)</f>
-        <v/>
-      </c>
-      <c r="K69" s="11" t="n">
+        <v>3600</v>
+      </c>
+      <c r="K69" s="14" t="n">
         <v>46306</v>
       </c>
-      <c r="L69" s="11" t="n">
-        <v>46307</v>
-      </c>
-      <c r="M69" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="N69" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="O69" s="9" t="s">
+      <c r="L69" s="14" t="n">
+        <v>46306</v>
+      </c>
+      <c r="M69" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="N69" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="O69" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E70" s="12" t="s">
         <v>27</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J70" s="12" t="n">
         <f aca="false">IF(I70="","",I70*3600)</f>
-        <v>1800</v>
+        <v>5400</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L70" s="14" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="M70" s="12" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="N70" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O70" s="12" t="s">
         <v>27</v>
@@ -5622,25 +5696,25 @@
     </row>
     <row r="71" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E71" s="12" t="s">
         <v>27</v>
       </c>
       <c r="F71" s="12" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G71" s="12" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="H71" s="12" t="n">
         <v>1</v>
@@ -5653,52 +5727,52 @@
         <v>1800</v>
       </c>
       <c r="K71" s="14" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L71" s="14" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="M71" s="12" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="N71" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O71" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E72" s="12" t="s">
         <v>27</v>
       </c>
       <c r="F72" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G72" s="12" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J72" s="12" t="n">
         <f aca="false">IF(I72="","",I72*3600)</f>
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="K72" s="14" t="n">
         <v>46307</v>
@@ -5707,87 +5781,81 @@
         <v>46307</v>
       </c>
       <c r="M72" s="12" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="N72" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O72" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="B73" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C73" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="D73" s="13" t="s">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D73" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="E73" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="F73" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G73" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="H73" s="12" t="n">
+      <c r="E73" s="9"/>
+      <c r="F73" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="H73" s="9"/>
+      <c r="I73" s="9"/>
+      <c r="J73" s="9" t="str">
+        <f aca="false">IF(I73="","",I73*3600)</f>
+        <v/>
+      </c>
+      <c r="K73" s="11" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L73" s="11" t="n">
+        <v>46307</v>
+      </c>
+      <c r="M73" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="N73" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="O73" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F74" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G74" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="H74" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="I73" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="12" t="n">
-        <f aca="false">IF(I73="","",I73*3600)</f>
-        <v>3600</v>
-      </c>
-      <c r="K73" s="14" t="n">
-        <v>46307</v>
-      </c>
-      <c r="L73" s="14" t="n">
-        <v>46307</v>
-      </c>
-      <c r="M73" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="N73" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="O73" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="B74" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="E74" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="F74" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G74" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="H74" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="I74" s="12" t="n">
         <v>0.5</v>
@@ -5797,80 +5865,90 @@
         <v>1800</v>
       </c>
       <c r="K74" s="14" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="L74" s="14" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="M74" s="12" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="N74" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O74" s="12" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="9" t="s">
+      <c r="A75" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="E75" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B75" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D75" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="H75" s="9"/>
-      <c r="I75" s="9"/>
-      <c r="J75" s="9" t="str">
+      <c r="F75" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G75" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="H75" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J75" s="12" t="n">
         <f aca="false">IF(I75="","",I75*3600)</f>
-        <v/>
-      </c>
-      <c r="K75" s="11"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="N75" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="O75" s="9" t="s">
+        <v>1800</v>
+      </c>
+      <c r="K75" s="14" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L75" s="14" t="n">
+        <v>46306</v>
+      </c>
+      <c r="M75" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="N75" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="O75" s="12" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E76" s="12" t="s">
         <v>29</v>
       </c>
       <c r="F76" s="12" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="G76" s="12" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="H76" s="12" t="n">
         <v>2</v>
@@ -5882,13 +5960,17 @@
         <f aca="false">IF(I76="","",I76*3600)</f>
         <v>3600</v>
       </c>
-      <c r="K76" s="14"/>
-      <c r="L76" s="14"/>
+      <c r="K76" s="14" t="n">
+        <v>46307</v>
+      </c>
+      <c r="L76" s="14" t="n">
+        <v>46307</v>
+      </c>
       <c r="M76" s="12" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="N76" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O76" s="12" t="s">
         <v>29</v>
@@ -5896,25 +5978,25 @@
     </row>
     <row r="77" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E77" s="12" t="s">
         <v>29</v>
       </c>
       <c r="F77" s="12" t="s">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="G77" s="12" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="H77" s="12" t="n">
         <v>2</v>
@@ -5926,13 +6008,17 @@
         <f aca="false">IF(I77="","",I77*3600)</f>
         <v>3600</v>
       </c>
-      <c r="K77" s="14"/>
-      <c r="L77" s="14"/>
+      <c r="K77" s="14" t="n">
+        <v>46307</v>
+      </c>
+      <c r="L77" s="14" t="n">
+        <v>46307</v>
+      </c>
       <c r="M77" s="12" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="N77" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O77" s="12" t="s">
         <v>29</v>
@@ -5940,202 +6026,202 @@
     </row>
     <row r="78" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E78" s="12" t="s">
         <v>29</v>
       </c>
       <c r="F78" s="12" t="s">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="G78" s="12" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J78" s="12" t="n">
         <f aca="false">IF(I78="","",I78*3600)</f>
-        <v>5400</v>
-      </c>
-      <c r="K78" s="14"/>
-      <c r="L78" s="14"/>
+        <v>1800</v>
+      </c>
+      <c r="K78" s="14" t="n">
+        <v>46307</v>
+      </c>
+      <c r="L78" s="14" t="n">
+        <v>46307</v>
+      </c>
       <c r="M78" s="12" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="N78" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O78" s="12" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="12" t="s">
-        <v>303</v>
-      </c>
-      <c r="B79" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C79" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D79" s="13" t="s">
+    <row r="79" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D79" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="E79" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F79" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="G79" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="H79" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I79" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J79" s="12" t="n">
+      <c r="E79" s="9"/>
+      <c r="F79" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="H79" s="9"/>
+      <c r="I79" s="9"/>
+      <c r="J79" s="9" t="str">
         <f aca="false">IF(I79="","",I79*3600)</f>
-        <v>5400</v>
-      </c>
-      <c r="K79" s="14"/>
-      <c r="L79" s="14"/>
-      <c r="M79" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="N79" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="O79" s="12" t="s">
-        <v>29</v>
+        <v/>
+      </c>
+      <c r="K79" s="11"/>
+      <c r="L79" s="11"/>
+      <c r="M79" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="N79" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="O79" s="9" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="D80" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F80" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G80" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="B80" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C80" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="D80" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="E80" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F80" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="G80" s="12" t="s">
-        <v>292</v>
-      </c>
       <c r="H80" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I80" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="I80" s="12" t="n">
-        <v>0.5</v>
       </c>
       <c r="J80" s="12" t="n">
         <f aca="false">IF(I80="","",I80*3600)</f>
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="K80" s="14"/>
       <c r="L80" s="14"/>
       <c r="M80" s="12" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="N80" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O80" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="9" t="s">
+      <c r="A81" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E81" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B81" s="9" t="s">
+      <c r="F81" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G81" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="H81" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C81" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D81" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="H81" s="9"/>
-      <c r="I81" s="9"/>
-      <c r="J81" s="9" t="str">
+      <c r="I81" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="12" t="n">
         <f aca="false">IF(I81="","",I81*3600)</f>
-        <v/>
-      </c>
-      <c r="K81" s="11" t="n">
-        <v>46307</v>
-      </c>
-      <c r="L81" s="11" t="n">
-        <v>46307</v>
-      </c>
-      <c r="M81" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="N81" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="O81" s="9" t="s">
+        <v>3600</v>
+      </c>
+      <c r="K81" s="14"/>
+      <c r="L81" s="14"/>
+      <c r="M81" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="N81" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="O81" s="12" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E82" s="12" t="s">
         <v>31</v>
       </c>
       <c r="F82" s="12" t="s">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="G82" s="12" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I82" s="12" t="n">
         <v>1.5</v>
@@ -6144,197 +6230,179 @@
         <f aca="false">IF(I82="","",I82*3600)</f>
         <v>5400</v>
       </c>
-      <c r="K82" s="14" t="n">
-        <v>46307</v>
-      </c>
-      <c r="L82" s="14" t="n">
-        <v>46307</v>
-      </c>
+      <c r="K82" s="14"/>
+      <c r="L82" s="14"/>
       <c r="M82" s="12" t="s">
-        <v>32</v>
+        <v>307</v>
       </c>
       <c r="N82" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O82" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="12" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E83" s="12" t="s">
         <v>31</v>
       </c>
       <c r="F83" s="12" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="G83" s="12" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J83" s="12" t="n">
         <f aca="false">IF(I83="","",I83*3600)</f>
-        <v>1800</v>
-      </c>
-      <c r="K83" s="14" t="n">
-        <v>46307</v>
-      </c>
-      <c r="L83" s="14" t="n">
-        <v>46307</v>
-      </c>
+        <v>5400</v>
+      </c>
+      <c r="K83" s="14"/>
+      <c r="L83" s="14"/>
       <c r="M83" s="12" t="s">
-        <v>32</v>
+        <v>307</v>
       </c>
       <c r="N83" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O83" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E84" s="12" t="s">
         <v>31</v>
       </c>
       <c r="F84" s="12" t="s">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="G84" s="12" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J84" s="12" t="n">
         <f aca="false">IF(I84="","",I84*3600)</f>
-        <v>7200</v>
-      </c>
-      <c r="K84" s="14" t="n">
-        <v>46307</v>
-      </c>
-      <c r="L84" s="14" t="n">
-        <v>46307</v>
-      </c>
+        <v>1800</v>
+      </c>
+      <c r="K84" s="14"/>
+      <c r="L84" s="14"/>
       <c r="M84" s="12" t="s">
-        <v>32</v>
+        <v>307</v>
       </c>
       <c r="N84" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O84" s="12" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="B85" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C85" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="D85" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="E85" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F85" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G85" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="H85" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I85" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="12" t="n">
+      <c r="A85" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D85" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="E85" s="9"/>
+      <c r="F85" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="H85" s="9"/>
+      <c r="I85" s="9"/>
+      <c r="J85" s="9" t="str">
         <f aca="false">IF(I85="","",I85*3600)</f>
-        <v>3600</v>
-      </c>
-      <c r="K85" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K85" s="11" t="n">
         <v>46307</v>
       </c>
-      <c r="L85" s="14" t="n">
+      <c r="L85" s="11" t="n">
         <v>46307</v>
       </c>
-      <c r="M85" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="N85" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="O85" s="12" t="s">
-        <v>31</v>
+      <c r="M85" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="N85" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="O85" s="9" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C86" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="E86" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F86" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G86" s="12" t="s">
         <v>324</v>
-      </c>
-      <c r="D86" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="E86" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F86" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G86" s="12" t="s">
-        <v>310</v>
       </c>
       <c r="H86" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J86" s="12" t="n">
         <f aca="false">IF(I86="","",I86*3600)</f>
-        <v>3600</v>
+        <v>5400</v>
       </c>
       <c r="K86" s="14" t="n">
         <v>46307</v>
@@ -6343,46 +6411,46 @@
         <v>46307</v>
       </c>
       <c r="M86" s="12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N86" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O86" s="12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="12" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F87" s="12" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G87" s="12" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="H87" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J87" s="12" t="n">
         <f aca="false">IF(I87="","",I87*3600)</f>
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="K87" s="14" t="n">
         <v>46307</v>
@@ -6391,92 +6459,106 @@
         <v>46307</v>
       </c>
       <c r="M87" s="12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N87" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O87" s="12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B88" s="9" t="s">
+    </row>
+    <row r="88" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="B88" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="E88" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F88" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G88" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="H88" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I88" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C88" s="10" t="s">
+      <c r="J88" s="12" t="n">
+        <f aca="false">IF(I88="","",I88*3600)</f>
+        <v>7200</v>
+      </c>
+      <c r="K88" s="14" t="n">
+        <v>46307</v>
+      </c>
+      <c r="L88" s="14" t="n">
+        <v>46307</v>
+      </c>
+      <c r="M88" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D88" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="E88" s="9"/>
-      <c r="F88" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="G88" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="H88" s="9"/>
-      <c r="I88" s="9"/>
-      <c r="J88" s="9" t="str">
-        <f aca="false">IF(I88="","",I88*3600)</f>
-        <v/>
-      </c>
-      <c r="K88" s="11"/>
-      <c r="L88" s="11"/>
-      <c r="M88" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="N88" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="O88" s="9" t="s">
+      <c r="N88" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="O88" s="12" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="12" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E89" s="12" t="s">
         <v>33</v>
       </c>
       <c r="F89" s="12" t="s">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="G89" s="12" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J89" s="12" t="n">
         <f aca="false">IF(I89="","",I89*3600)</f>
-        <v>10800</v>
-      </c>
-      <c r="K89" s="14"/>
-      <c r="L89" s="14"/>
+        <v>3600</v>
+      </c>
+      <c r="K89" s="14" t="n">
+        <v>46307</v>
+      </c>
+      <c r="L89" s="14" t="n">
+        <v>46307</v>
+      </c>
       <c r="M89" s="12" t="s">
-        <v>331</v>
+        <v>34</v>
       </c>
       <c r="N89" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O89" s="12" t="s">
         <v>33</v>
@@ -6484,56 +6566,234 @@
     </row>
     <row r="90" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="12" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D90" s="13" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E90" s="12" t="s">
         <v>33</v>
       </c>
       <c r="F90" s="12" t="s">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="G90" s="12" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J90" s="12" t="n">
         <f aca="false">IF(I90="","",I90*3600)</f>
-        <v>14400</v>
-      </c>
-      <c r="K90" s="14"/>
-      <c r="L90" s="14"/>
+        <v>3600</v>
+      </c>
+      <c r="K90" s="14" t="n">
+        <v>46307</v>
+      </c>
+      <c r="L90" s="14" t="n">
+        <v>46307</v>
+      </c>
       <c r="M90" s="12" t="s">
-        <v>331</v>
+        <v>34</v>
       </c>
       <c r="N90" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O90" s="12" t="s">
         <v>33</v>
       </c>
     </row>
+    <row r="91" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F91" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G91" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="H91" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" s="12" t="n">
+        <f aca="false">IF(I91="","",I91*3600)</f>
+        <v>3600</v>
+      </c>
+      <c r="K91" s="14" t="n">
+        <v>46307</v>
+      </c>
+      <c r="L91" s="14" t="n">
+        <v>46307</v>
+      </c>
+      <c r="M91" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="N91" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="O91" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="E92" s="9"/>
+      <c r="F92" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="G92" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="H92" s="9"/>
+      <c r="I92" s="9"/>
+      <c r="J92" s="9" t="str">
+        <f aca="false">IF(I92="","",I92*3600)</f>
+        <v/>
+      </c>
+      <c r="K92" s="11"/>
+      <c r="L92" s="11"/>
+      <c r="M92" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="N92" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="O92" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="B93" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="D93" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F93" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G93" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="H93" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I93" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J93" s="12" t="n">
+        <f aca="false">IF(I93="","",I93*3600)</f>
+        <v>10800</v>
+      </c>
+      <c r="K93" s="14"/>
+      <c r="L93" s="14"/>
+      <c r="M93" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="N93" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="O93" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="E94" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F94" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G94" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="H94" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I94" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J94" s="12" t="n">
+        <f aca="false">IF(I94="","",I94*3600)</f>
+        <v>14400</v>
+      </c>
+      <c r="K94" s="14"/>
+      <c r="L94" s="14"/>
+      <c r="M94" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="N94" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="O94" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O90"/>
+  <autoFilter ref="A1:O94"/>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="N2:N90" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="N2:N94" type="list">
       <formula1>"To Do,In Progress,Done"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F90" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F94" type="list">
       <formula1>"Highest,High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6562,42 +6822,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6605,12 +6865,12 @@
     </row>
     <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
